--- a/SLIDE_MANIFEST.template.xlsx
+++ b/SLIDE_MANIFEST.template.xlsx
@@ -16248,7 +16248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -16357,17 +16357,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>A12.{month}.Swipes</t>
+          <t>A16.7.{month}</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Responder Swipes (per month)</t>
+          <t>Spend + Swipe Trajectory (per month, paired with A13)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Line chart</t>
+          <t>Combo line</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -16383,9 +16383,9 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -16393,12 +16393,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>A12.{month}.Spend</t>
+          <t>A12.{month}.Swipes</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Responder Spend (per month)</t>
+          <t>Responder Swipes (per month)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -16429,17 +16429,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>A14.2</t>
+          <t>A12.{month}.Spend</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Responder Account Age Distribution</t>
+          <t>Responder Spend (per month)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bar chart</t>
+          <t>Line chart</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
@@ -16465,17 +16465,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>A13.Agg</t>
+          <t>A14.2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>All-Time Mailer Summary</t>
+          <t>Responder Account Age Distribution</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Mailer summary</t>
+          <t>Bar chart</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>mailer_summary</t>
+          <t>screenshot</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -16501,17 +16501,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>A13.5</t>
+          <t>A13.Agg</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Responder Count Trend</t>
+          <t>All-Time Mailer Summary</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Stacked bar</t>
+          <t>Mailer summary</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -16524,7 +16524,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>screenshot</t>
+          <t>mailer_summary</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -16537,17 +16537,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>A13.6</t>
+          <t>A13.5</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Response Rate Trend</t>
+          <t>Responder Count Trend</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Line chart</t>
+          <t>Stacked bar</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -16573,12 +16573,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>A15.1</t>
+          <t>A13.6</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Market Reach: Program Penetration</t>
+          <t>Response Rate Trend</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -16609,25 +16609,25 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A15.2</t>
+          <t>A15.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Spend Share: Responder vs Non-Responder</t>
+          <t>Market Reach: Program Penetration</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Grouped bar</t>
+          <t>Line chart</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>TWO_CONTENT</t>
+          <t>CUSTOM</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -16645,25 +16645,25 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>A15.3</t>
+          <t>A15.2</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Revenue Attribution</t>
+          <t>Spend Share: Responder vs Non-Responder</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Waterfall</t>
+          <t>Grouped bar</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>CUSTOM</t>
+          <t>TWO_CONTENT</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -16681,25 +16681,25 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>A15.4</t>
+          <t>A15.3</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Pre/Post Spend Delta</t>
+          <t>Revenue Attribution</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Grouped bar</t>
+          <t>Waterfall</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>TWO_CONTENT</t>
+          <t>CUSTOM</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -16717,25 +16717,25 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>A16.1</t>
+          <t>A15.4</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Cohort Trajectory: Swipes (Recent)</t>
+          <t>Pre/Post Spend Delta</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Line chart</t>
+          <t>Grouped bar</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>CUSTOM</t>
+          <t>TWO_CONTENT</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -16753,12 +16753,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>A16.2</t>
+          <t>A16.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Cohort Trajectory: Swipes (All)</t>
+          <t>Cohort Trajectory: Swipes (Recent)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -16789,12 +16789,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>A16.3</t>
+          <t>A16.2</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Cohort Trajectory: Spend (Recent)</t>
+          <t>Cohort Trajectory: Swipes (All)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -16825,12 +16825,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>A16.4</t>
+          <t>A16.3</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Cohort Trajectory: Spend (All)</t>
+          <t>Cohort Trajectory: Spend (Recent)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -16861,12 +16861,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>A16.5</t>
+          <t>A16.4</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Cohort Trajectory: Items (Recent)</t>
+          <t>Cohort Trajectory: Spend (All)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>A16.6</t>
+          <t>A16.5</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Cohort Trajectory: Items (All)</t>
+          <t>Cohort Trajectory: Items (Recent)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -16933,12 +16933,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>A17.1</t>
+          <t>A16.6</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Cumulative Reach: Accounts</t>
+          <t>Cohort Trajectory: Items (All)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -16969,17 +16969,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>A17.2</t>
+          <t>A17.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Cumulative Reach: By Segment</t>
+          <t>Cumulative Reach: Accounts</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Stacked area</t>
+          <t>Line chart</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
@@ -17005,17 +17005,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>A17.3</t>
+          <t>A17.2</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Cumulative Reach: Response Rate Over Time</t>
+          <t>Cumulative Reach: By Segment</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Line chart</t>
+          <t>Stacked area</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
@@ -17034,6 +17034,42 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>A17.3</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Cumulative Reach: Response Rate Over Time</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
